--- a/Sample form for Product list - Copy.xlsx
+++ b/Sample form for Product list - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A1A8C5-58DF-453A-A4D5-BA67D84D2403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B76911-E5AF-4647-B3E3-43666F596C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="1060" windowWidth="23060" windowHeight="12080" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPVC Equal SKUs" sheetId="1" r:id="rId1"/>
@@ -2527,7 +2527,7 @@
   <cols>
     <col min="1" max="1" width="36.26953125" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7265625" style="11" customWidth="1"/>
-    <col min="3" max="8" width="17" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="7.453125" style="11" customWidth="1"/>
     <col min="9" max="17" width="16.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="18" max="33" width="16.1796875" style="11" bestFit="1" customWidth="1"/>
     <col min="34" max="36" width="16" style="11" bestFit="1" customWidth="1"/>
